--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="277">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette section regroupe les résultats d'examens (biologie polyvalente, imagerie, cytologie, pathologie, génétique humaine...)</t>
+    <t>Cette section regroupe les rÃ©sultats d'examens (biologie polyvalente, imagerie, cytologie, pathologie, gÃ©nÃ©tique humaine...)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -408,7 +408,7 @@
     <t>frSectionResultats</t>
   </si>
   <si>
-    <t>Conformité de la section aux spécifications CI-SIS</t>
+    <t>ConformitÃ© de la section aux spÃ©cifications CI-SIS</t>
   </si>
   <si>
     <t>Section.templateId:frSectionResultats.nullFlavor</t>
@@ -475,10 +475,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -554,7 +557,7 @@
     <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
   </si>
   <si>
-    <t>Résultats d’examens</t>
+    <t>RÃ©sultats dâ€™examens</t>
   </si>
   <si>
     <t>CD.displayName</t>
@@ -687,7 +690,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée FR-Resultats</t>
+    <t>EntrÃ©e FR-Resultats</t>
   </si>
   <si>
     <t>Section.entry.nullFlavor</t>
@@ -3275,7 +3278,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>148</v>
       </c>
@@ -3288,13 +3291,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3305,8 +3308,12 @@
       <c r="K21" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="L21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3376,10 +3383,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3393,7 +3400,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3402,13 +3409,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3459,7 +3466,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3479,10 +3486,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3578,12 +3585,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3593,13 +3600,13 @@
         <v>62</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -3612,7 +3619,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3624,7 +3631,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3663,7 +3670,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3681,28 +3688,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3715,7 +3722,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3727,7 +3734,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3766,7 +3773,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3786,17 +3793,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3818,7 +3825,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3830,7 +3837,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -3869,7 +3876,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3889,17 +3896,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3921,7 +3928,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3972,7 +3979,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3990,28 +3997,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4024,7 +4031,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4036,7 +4043,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -4075,7 +4082,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4095,10 +4102,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4121,11 +4128,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4176,7 +4183,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4196,10 +4203,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4226,7 +4233,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4277,7 +4284,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4297,17 +4304,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4325,11 +4332,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4380,7 +4387,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4400,17 +4407,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4428,11 +4435,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4483,7 +4490,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4503,17 +4510,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4531,11 +4538,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4586,7 +4593,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4606,10 +4613,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4623,7 +4630,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4632,13 +4639,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4689,7 +4696,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4709,10 +4716,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4726,7 +4733,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4735,13 +4742,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4792,7 +4799,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4812,10 +4819,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4838,7 +4845,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -4891,7 +4898,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4911,10 +4918,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4970,25 +4977,25 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5008,10 +5015,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5034,7 +5041,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -5087,7 +5094,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5107,10 +5114,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5133,7 +5140,7 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -5186,7 +5193,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5206,10 +5213,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5232,7 +5239,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -5285,7 +5292,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5305,10 +5312,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5322,7 +5329,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5331,10 +5338,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5386,7 +5393,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5406,10 +5413,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5507,10 +5514,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5608,10 +5615,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5709,10 +5716,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5810,10 +5817,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5913,10 +5920,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6016,10 +6023,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6119,10 +6126,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6222,10 +6229,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6323,10 +6330,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6356,7 +6363,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
@@ -6382,7 +6389,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6400,7 +6407,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6420,10 +6427,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6457,7 +6464,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>74</v>
@@ -6499,7 +6506,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6519,10 +6526,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6545,7 +6552,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6598,7 +6605,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6618,10 +6625,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6644,7 +6651,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6697,7 +6704,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6717,10 +6724,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6743,7 +6750,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6796,7 +6803,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6816,10 +6823,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6842,7 +6849,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6895,7 +6902,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -6915,10 +6922,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6941,7 +6948,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6994,7 +7001,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7014,10 +7021,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7040,7 +7047,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7093,7 +7100,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7113,10 +7120,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7139,7 +7146,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7192,7 +7199,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7212,10 +7219,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7238,7 +7245,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7291,7 +7298,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7311,10 +7318,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7337,7 +7344,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7390,7 +7397,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7410,10 +7417,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7436,7 +7443,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7489,7 +7496,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7509,10 +7516,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7610,10 +7617,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7711,10 +7718,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7812,10 +7819,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7913,10 +7920,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8016,10 +8023,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8119,10 +8126,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8222,10 +8229,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8325,10 +8332,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8426,10 +8433,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8456,7 +8463,7 @@
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8465,7 +8472,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>74</v>
@@ -8507,7 +8514,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8527,10 +8534,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8564,7 +8571,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>74</v>
@@ -8606,7 +8613,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8626,10 +8633,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8652,7 +8659,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8705,7 +8712,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-section-resultats.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
